--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E589C082-3E14-A24D-B77D-882E21B39304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39B28AC-620F-7240-BECF-BC919F20DF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11880" yWindow="2280" windowWidth="28060" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="9160" yWindow="1140" windowWidth="28060" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -502,6 +502,79 @@
    &lt;li&gt;誰來解決？：需要桃園市政府，區域民意代表, 里長, 社區管委會 共同努力，為社區住戶謀取基本的生活條件 - 空氣品質的安全保障！也需要區域居民的全民參與爭取我們共同的基本生活環境-空氣品質的提升。&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20211025A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境保護</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>污水處理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A7重劃區最早的建案目前污水處理功能仍尚未啟動。已經進駐第三年的社區，何時才能啟動污水處理系統？我們以往產生的污水排放到哪裡了？&lt;br&gt;
+依據社區網站資訊：
+&lt;ul&gt;
+   &lt;li&gt; &lt;a href="https://tcwang.github.io/A7Xinlinkou/A7XLK-24-FloodPrevention.html#Menu-B5"&gt;污水下水道&lt;/a&gt;：桃園市整體污水下水道建制只有67.2%, 而A7重劃區屬於具備污水下水道的區域。
+   &lt;/li&gt;
+   &lt;li&gt;依據桃園市水務局 &lt;a href="https://wrb.tycg.gov.tw/home.jsp?id=519&amp;parentpath=0,177,490,512"&gt;A7站地區下水道系統&lt;/a&gt;, 
+    &lt;a href="https://sewergis.tycg.gov.tw/Account/Login"&gt;管線及用戶查詢&lt;/a&gt;: 目前區段徵收地區已約有4,000戶完成設置切換閥與管線連通，待水資中心完成後，即可通水處理。
+   &lt;/li&gt;
+   &lt;li&gt; 目前A7重劃區已進駐社區, 已完成切換閥與管線聯通作業，為何進駐第三年還未能進行污水處理。而這些污水是否已造成附近環境污染？
+   &lt;/li&gt;
+&lt;/ul&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20211025B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建商爭議</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法律諮詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本案件是在某社區第三年的區分所有權人會議上提出討論，作業方向為
+&lt;ul&gt;
+   &lt;li&gt;長庚里里長全程參與社區會議，並解答此案長庚里 已經在與市府相關單位協調中。感謝長庚里 林俊源里長的社區服務！
+   &lt;/li&gt;
+   &lt;li&gt;本案牽涉所有A7重劃區社區住戶，應該有市議員能協助 調查整體作業進度為何延宕三年無法啟用？是否造成附近水資源污染？應要求市府相關單位提供具體污水處理啟用時程！
+   &lt;/li&gt;
+&lt;/ul&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A7重劃區某社區的公設點交因建商一再拖延改善作業，造成
+&lt;ul&gt;
+   &lt;li&gt;管委會是委託驗屋公司執行公共設施的驗收。而驗屋查到的缺點建設公司沒有積極處理，以致造成原有規劃的公共設施擺爛無法使用。
+   &lt;/li&gt;
+   &lt;li&gt;住戶進駐第三年都無法使用公共設施,  如運動器材，影音器材空置三年可能都生鏽成廢品。每一住戶的押金也無法退還。造成住戶財務及生活上極大的損失。
+   &lt;/li&gt;
+   &lt;li&gt;管委會委員為義務公共服務性質，無法代表全社區做有效的履約談判。社區主委也未必有相關知識與經驗去應對供應商不作為的惡劣態度。
+   &lt;/li&gt;
+&lt;/ul&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>對本案之處理，仍須集思廣益：包含
+&lt;ul&gt;
+   &lt;li&gt; 供應商應該有基本屢行售後服務的責任。尤其不止單一建案的建商, 應改考量網路上商譽的衝擊。及早誠意解決公共設施缺失改善。
+   &lt;/li&gt;
+   &lt;li&gt; 驗屋公司往往鉅細彌遺找出缺點，但部分缺失如磁磚貼合問題，如果有小問題將該磁磚挖掉重新貼未必是好的方法。也許可以對僅止於美觀或小瑕疵，能有扣款結案的機制。但需要有相關扣款額度的大數據支持。讓相關作業能依據公訂價格處理？
+   &lt;/li&gt;
+   &lt;li&gt; 管委會主委未必是有此經驗去應對建商, 需能向相關單位尋求協助。如每個議員都有法律顧問的諮詢服務，是否諮詢議員的法律顧問來協助做有效處理？
+   &lt;/li&gt;
+&lt;/ul&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -919,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BF8730-3384-6948-B66D-EC2DE92401CC}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -974,109 +1047,167 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="409.6">
+    <row r="2" spans="1:20" ht="395">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="9">
-        <v>44336.390277777777</v>
+        <v>44494.326388888891</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" s="10">
-        <v>44336</v>
+        <v>44494</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="304">
+    <row r="3" spans="1:20" ht="288">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="9">
-        <v>44330.719444444447</v>
+        <v>44494.329861111109</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F3" s="10">
-        <v>44330</v>
+        <v>44494</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="409.6">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="9">
+        <v>44336.390277777777</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="10">
+        <v>44336</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="304">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9">
+        <v>44330.719444444447</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="10">
+        <v>44330</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="409.6">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5">
         <v>44327.25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F6" s="2">
         <v>44327</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39B28AC-620F-7240-BECF-BC919F20DF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32826B9F-7F03-5D47-8CE6-2D4AC7AE443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9160" yWindow="1140" windowWidth="28060" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="3560" yWindow="940" windowWidth="34260" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -574,6 +574,13 @@
    &lt;/li&gt;
    &lt;li&gt; 管委會主委未必是有此經驗去應對建商, 需能向相關單位尋求協助。如每個議員都有法律顧問的諮詢服務，是否諮詢議員的法律顧問來協助做有效處理？
    &lt;/li&gt;
+&lt;/ul&gt;
+本案例應該注意, 並應請求法律諮詢的事項
+&lt;ul&gt;
+   &lt;li&gt;民法 施工瑕疵修補, 減價及驗收爭議 ：請求權 在瑕疵發現期間5年, 目前已過3年。建商只要再拖2年 社區就會喪失請求修補權？
+   &lt;/li&gt;
+   &lt;li&gt; 當瑕疵修補長期無法達成時，住戶管委會代表應該儘速尋求減少報酬, 損害賠償等方向著手。避免應不暸解法規陷入喪失請求權時限或保固期限。
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1076,7 +1083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="288">
+    <row r="3" spans="1:20" ht="350">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32826B9F-7F03-5D47-8CE6-2D4AC7AE443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C850E842-CD61-514F-A705-6AAFC5EAE281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="940" windowWidth="34260" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="-34320" yWindow="7720" windowWidth="34260" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C850E842-CD61-514F-A705-6AAFC5EAE281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4A2967-1F14-3E4F-A5A6-F39C18E6B023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34320" yWindow="7720" windowWidth="34260" windowHeight="19420" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="-14080" yWindow="-19720" windowWidth="27960" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -543,16 +543,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本案件是在某社區第三年的區分所有權人會議上提出討論，作業方向為
-&lt;ul&gt;
-   &lt;li&gt;長庚里里長全程參與社區會議，並解答此案長庚里 已經在與市府相關單位協調中。感謝長庚里 林俊源里長的社區服務！
-   &lt;/li&gt;
-   &lt;li&gt;本案牽涉所有A7重劃區社區住戶，應該有市議員能協助 調查整體作業進度為何延宕三年無法啟用？是否造成附近水資源污染？應要求市府相關單位提供具體污水處理啟用時程！
-   &lt;/li&gt;
-&lt;/ul&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">A7重劃區某社區的公設點交因建商一再拖延改善作業，造成
 &lt;ul&gt;
    &lt;li&gt;管委會是委託驗屋公司執行公共設施的驗收。而驗屋查到的缺點建設公司沒有積極處理，以致造成原有規劃的公共設施擺爛無法使用。
@@ -581,6 +571,46 @@
    &lt;/li&gt;
    &lt;li&gt; 當瑕疵修補長期無法達成時，住戶管委會代表應該儘速尋求減少報酬, 損害賠償等方向著手。避免應不暸解法規陷入喪失請求權時限或保固期限。
   &lt;/li&gt;
+&lt;/ul&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22020321A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社區管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化社區管理效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;h3&gt;如何強化社區管理?  &lt;/h3&gt;
+以下是對社區管理相關的網路文章匯總整理,  希望有更多正面意見來讓社區管理更好！ &lt;br&gt;&lt;br&gt;
+&lt;h5&gt;網民對管委會主委的看法整理&lt;/h5&gt;
+　　很多人都認為只要選上社區主委或當上社區管委會的委員，就自以為像擁有社區權貴級的權力。雖然主委是法定的社區最高代表人，也是最大權力者，但社區主委或管委會委員，只有「管理、督促或協調」之責，並沒有任何實質的公權力，當因協調不成而需要行使任何權力時（如：強制拆除），必需交由警政單位或報請主管機關處理。主委或管委會任一委員絕對沒有任何權力可以親自執行。
+&lt;br&gt;&lt;br&gt;
+　　很多社區主委會出現這樣"權貴"的假象跟保全公司有關聯，最常看到的是社區的總幹事或保全人員，每當一看到主委或管委會任一委員出現在社區時，會以"貴賓"般的禮遇對待。保全公司當然認主委及管理委員為自己的衣食父母。但保全公司是否該真正想過，其實自己的衣食父母，就是社區的所有住戶，維護社區安全及所有住戶權益才是最大的職責。
+&lt;br&gt;&lt;br&gt;
+　　在法律上，主委代表全社區，主委要必須概括承受管委會所有的法律責任，包括刑責也在內！權力固然大，但是為了讓社區及住戶更好才是。更應本著服務社區的態度，而非濫用職權、頤指氣使，不過當社區的主委或委員都是無給職的，社區裡的事務很多都是吃力不討好，住戶有時也該多多體諒主委，共同為社區努力，社區才會更美好。
+&lt;br&gt;&lt;br&gt;
+　　對社區議案往往都有正反兩種意見, 當表決後需要執行多數意見時。就會造成反對者對管委會尤其主委的怨懟。如停車管理, 社區公共空間的管理，如果採用較嚴格的管理自然會有住戶無法在自家汽車停車格改停機車或自行車。當多數住戶都有機車停車位不足時，管委會無暇為公共議題多作考量。但許多公共議題需要有社區代表統合出面向地方/議員爭取！管委會主委往往忽視與浪費了自身主委的社區代表身份。又如公共設施的驗收/與建商爭議的協商，居民無法各自行動，主委是責無旁貸的法定代表！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;h5&gt;如何改善社區管理 &lt;/h5&gt;
+本項議題希望 開放網路討論, 集思廣益建立社區的正向發展。包含
+&lt;ul&gt;
+&lt;li&gt;社區住戶的意見表達, 交流與彙總需要有即時的網路溝通管道, 目前 社區管理APP 多數管委會是採用免費軟件。沒有較好的功能外多數成為廠商的廣告平台附加品，以致缺少有效的意見溝通與交流。當遇到重大議題需要招開會議時又會遇到法定開會人數不足，或冗長討論之無效率管理降低住戶參與的熱情。  &lt;/li&gt;
+&lt;li&gt;社區志工團隊的建構, 管委會委員及主委是無給兼職。住戶多數事務需要更多的居民能以志工形式來分擔。但主導志工團隊仍須管委會來主導成立。否則熱心住戶對相關議題只能愛莫能助? 
+而管委會委員/主委只能自怨自艾造成無效能的社區管理。 &lt;/li&gt;
+&lt;li&gt;其他改善社區管理的意見仍待網民 提供 &lt;/li&gt;
 &lt;/ul&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -999,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BF8730-3384-6948-B66D-EC2DE92401CC}">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -1054,167 +1084,196 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="395">
+    <row r="2" spans="1:20" ht="110" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="9">
-        <v>44494.326388888891</v>
+        <v>110384.34097222223</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F2" s="10">
-        <v>44494</v>
+        <v>44641</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="350">
+    <row r="3" spans="1:20" ht="395">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="9">
-        <v>44494.329861111109</v>
+        <v>44494.326388888891</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F3" s="10">
         <v>44494</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="409.6">
+    <row r="4" spans="1:20" ht="350">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="9">
-        <v>44336.390277777777</v>
+        <v>44494.329861111109</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F4" s="10">
-        <v>44336</v>
+        <v>44494</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="304">
+    <row r="5" spans="1:20" ht="409.6">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="9">
-        <v>44330.719444444447</v>
+        <v>44336.390277777777</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F5" s="10">
-        <v>44330</v>
+        <v>44336</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="409.6">
+    <row r="6" spans="1:20" ht="304">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="9">
+        <v>44330.719444444447</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="10">
+        <v>44330</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="409.6">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
         <v>44327.25</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F7" s="2">
         <v>44327</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4A2967-1F14-3E4F-A5A6-F39C18E6B023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A719D3A9-B1DE-4741-8571-4D91AF30194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14080" yWindow="-19720" windowWidth="27960" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A719D3A9-B1DE-4741-8571-4D91AF30194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3822D4F7-283D-9B4E-BF0A-1F22A0F3498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14080" yWindow="-19720" windowWidth="27960" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -396,30 +396,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>社區交通違規案件檢討包含：
-&lt;ul&gt;
-    &lt;li&gt;附近的報廢車輛被改成建商的免費廣告，都沒有車牌且部分玻璃碎裂輪胎刺破。嚴重影響市容觀瞻。&lt;/li&gt;
-&lt;/ul&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市交通違規檢舉 QRcode :點擊或掃描
-&lt;a href="https://tvrweb.typd.gov.tw:3443/TTPB/D0101"&gt;
-   &lt;img  src="fig/XLK-2203-ANC/ANC-20210514-01.png", class="img-fluid, style="width:150px"&gt;
-&lt;/a&gt;&lt;br&gt;
-	桃園市政府警察局：&lt;a href="https://tvrweb.typd.gov.tw:3443/"&gt;
-	交通違規檢舉專區&lt;/a&gt; &lt;br&gt;檢舉說明
-	&lt;ol&gt;
-		&lt;li&gt;違規車輛號牌：違規車號清晰可辨及車輛顏色。&lt;/li&gt;
-		&lt;li&gt;違規事實：應攝入相關標誌、標線或地點；如為標線，顏色須清楚可辨；車輛駕駛人是否在場（以辦識該車屬臨時停車或停車之狀態&lt;/li&gt;
-		&lt;li&gt;違規時之日期及時間。&lt;/li&gt;
-	&lt;/ol&gt;
-	使用含日期地點的照相軟體作為舉證依據: 時間相機App &lt;a href="https://play.google.com/store/apps/details?id=com.jeyluta.timestampcamerafree&amp;hl=zh_TW&amp;gl=US"&gt;Google Play&lt;/a&gt;,
-	&lt;a href="https://apps.apple.com/tw/app/%E6%99%82%E9%96%93%E7%9B%B8%E6%A9%9F/id840110184"&gt;App Store&lt;/a&gt;
-&lt;br&gt;&lt;br&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>&lt;p&gt;
 A7</t>
@@ -485,15 +461,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>將依據社群訴求做匯總如下， 詳細內容請參考環境保護 / 異味管制辦法中 &lt;a href="https://tcwang.github.io/A7Xinlinkou/A7XLK-23-EnvironmentalProtection.html#Menu-B2"&gt;  辦法草案 &lt;/a&gt;, 作業要點如下
-&lt;ul&gt;
-   &lt;li&gt;由環保局強力介入華亞園區 固定污染源的管控, 協助廠商建立有效的製程VOCs 管控改善辦法, 建立該廠區對TVOC 的監測設備。定期公布VOC排放總量做數據化管控。   &lt;/li&gt;
-   &lt;li&gt;由市政府在住宅與工廠鄰近區域依據季節性風向，建立具備TVOC 偵測的空氣盒子/微型偵測儀物聯網。數量需能有效防堵與 全面管控園區內固定污染源 TVOC的 排放避免擴散至住宅區。&lt;/li&gt;
-   &lt;li&gt;由桃園市政府 建立異味管制有效措施，如異味舉報處理流程（參考歐美的投訴標準及處理流程）, 建立異味安全距離管控（檢討住宅與工廠區的安全距離），建立工業園區/科學園區 VOC 污染區域模型分析,總量管制等。邀請學者專家檢討我國TVOC 相關法規與國際標準的差異，是否需要修法等問題。  &lt;/li&gt;
-&lt;/ul&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">多年來A7重劃區發生的異味污染陳情案件, 仍沒有獲得有效處理。2020年媒體披露相關異味污染問題及環保局處理困難, 如: &lt;a href="https://udn.com/news/story/7324/4855906"&gt;聯合新聞網 2020/09/13&lt;/a&gt;, &lt;a href="https://news.ltn.com.tw/news/life/paper/1398916"&gt;自由時報 2020/09/11&lt;/a&gt;。 整體問題及相關資訊整理在 &lt;a href="https://tcwang.github.io/A7Xinlinkou/A7XLK-23-EnvironmentalProtection.html#Menu-B2"&gt;異味防制辦法&lt;/a&gt;, 其中要點包含
 &lt;ul&gt;
    &lt;li&gt;異味發生的主因：依據相關資訊 異味應該起因於華亞園區某公司 對揮發性有機溶劑VOCs 未能有效管制所引起(待驗證）。同時該公司直到2020年仍有多起違反空氣污染法相關條文的裁罰處分的紀錄。&lt;/li&gt;
@@ -612,6 +579,43 @@
 而管委會委員/主委只能自怨自艾造成無效能的社區管理。 &lt;/li&gt;
 &lt;li&gt;其他改善社區管理的意見仍待網民 提供 &lt;/li&gt;
 &lt;/ul&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社區交通違規案件檢討包含：
+&lt;ul&gt;
+    &lt;li&gt;A7附近的報廢車輛被改成建商的免費廣告，都沒有車牌且部分玻璃碎裂輪胎刺破。嚴重影響市容觀瞻。&lt;/li&gt;
+    &lt;li&gt;甲子園社區附近的紅線違停超級嚴重，早上尖峰時段，紅線車「群」直接擋住一半的車道&lt;/li&gt;
+&lt;/ul&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">將依據社群訴求做匯總如下， 詳細內容請參考環境保護 / 異味管制辦法中 &lt;a href="https://tcwang.github.io/A7Xinlinkou/A7XLK-23-EnvironmentalProtection.html#Menu-B2"&gt;  辦法草案 &lt;/a&gt;, 作業要點如下
+&lt;ul&gt;
+   &lt;li&gt;由環保局強力介入華亞園區 固定污染源的管控, 協助廠商建立有效的製程VOCs 管控改善辦法, 建立該廠區對TVOC 的監測設備。定期公布VOC排放總量做數據化管控。   &lt;/li&gt;
+   &lt;li&gt;由市政府在住宅與工廠鄰近區域依據季節性風向，建立具備TVOC 偵測的空氣盒子/微型偵測儀物聯網。數量需能有效防堵與 全面管控園區內固定污染源 TVOC的 排放避免擴散至住宅區。&lt;/li&gt;
+   &lt;li&gt;由桃園市政府 建立異味管制有效措施，如異味舉報處理流程（參考歐美的投訴標準及處理流程）, 建立異味安全距離管控（檢討住宅與工廠區的安全距離），建立工業園區/科學園區 VOC 污染區域模型分析,總量管制等。邀請學者專家檢討我國TVOC 相關法規與國際標準的差異，是否需要修法等問題。  &lt;/li&gt;
+&lt;/ul&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A. 請居民直接向桃園市交通違規檢舉 QRcode :點擊或掃描
+&lt;a href="https://tvrweb.typd.gov.tw:3443/TTPB/D0101"&gt;
+   &lt;img  src="fig/XLK-2203-ANC/ANC-20210514-01.png", class="img-fluid, style="width:150px"&gt;
+&lt;/a&gt;&lt;br&gt;
+	桃園市政府警察局：&lt;a href="https://tvrweb.typd.gov.tw:3443/"&gt;
+	交通違規檢舉專區&lt;/a&gt; &lt;br&gt;檢舉說明
+	&lt;ol&gt;
+		&lt;li&gt;違規車輛號牌：違規車號清晰可辨及車輛顏色。&lt;/li&gt;
+		&lt;li&gt;違規事實：應攝入相關標誌、標線或地點；如為標線，顏色須清楚可辨；車輛駕駛人是否在場（以辦識該車屬臨時停車或停車之狀態&lt;/li&gt;
+		&lt;li&gt;違規時之日期及時間。&lt;/li&gt;
+	&lt;/ol&gt;
+	使用含日期地點的照相軟體作為舉證依據: 時間相機App &lt;a href="https://play.google.com/store/apps/details?id=com.jeyluta.timestampcamerafree&amp;hl=zh_TW&amp;gl=US"&gt;Google Play&lt;/a&gt;,
+	&lt;a href="https://apps.apple.com/tw/app/%E6%99%82%E9%96%93%E7%9B%B8%E6%A9%9F/id840110184"&gt;App Store&lt;/a&gt;
+&lt;br&gt;&lt;br&gt;
+B. 因交通違規檢舉項目限縮, 無法直接舉報的違規項目仍可 請里長/議員 能統籌向轄區警察局報請取締。
+&lt;br&gt;&lt;br&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1086,7 +1090,7 @@
     </row>
     <row r="2" spans="1:20" ht="110" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1098,24 +1102,24 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" s="10">
         <v>44641</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="395">
       <c r="A3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1127,24 +1131,24 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" s="10">
         <v>44494</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="350">
       <c r="A4" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1156,24 +1160,24 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F4" s="10">
         <v>44494</v>
       </c>
       <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="409.6">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1185,22 +1189,22 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" s="10">
         <v>44336</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="304">
+    <row r="6" spans="1:20" ht="350">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
@@ -1223,10 +1227,10 @@
         <v>20</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="409.6">
@@ -1249,10 +1253,10 @@
         <v>44327</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
@@ -1264,7 +1268,7 @@
         <v>16</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3822D4F7-283D-9B4E-BF0A-1F22A0F3498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF409A00-0034-3A43-A521-215CF3C8B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -616,6 +616,44 @@
 &lt;br&gt;&lt;br&gt;
 B. 因交通違規檢舉項目限縮, 無法直接舉報的違規項目仍可 請里長/議員 能統籌向轄區警察局報請取締。
 &lt;br&gt;&lt;br&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20220611A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陽台加窗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>住家陽台是否能加強防風遮雨等功能？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
+&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
+&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
+&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
+&lt;h5&gt;雙北及桃園 2006年以後的規定&lt;/h5&gt;
+但為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
+管委會同意且經縣市政府通過可以加窗門窗者，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
+另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
+受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
+&lt;br&gt;&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1033,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BF8730-3384-6948-B66D-EC2DE92401CC}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -1088,196 +1126,225 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="110" customHeight="1">
+    <row r="2" spans="1:20" ht="409.6">
       <c r="A2" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="9">
-        <v>110384.34097222223</v>
+        <v>44723.25</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F2" s="10">
-        <v>44641</v>
+        <v>44723</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="395">
+    <row r="3" spans="1:20" ht="110" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="9">
-        <v>44494.326388888891</v>
+        <v>110384.34097222223</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F3" s="10">
-        <v>44494</v>
+        <v>44641</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="350">
+    <row r="4" spans="1:20" ht="395">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="9">
-        <v>44494.329861111109</v>
+        <v>44494.326388888891</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F4" s="10">
         <v>44494</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="409.6">
+    <row r="5" spans="1:20" ht="350">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="9">
-        <v>44336.390277777777</v>
+        <v>44494.329861111109</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F5" s="10">
-        <v>44336</v>
+        <v>44494</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="350">
+    <row r="6" spans="1:20" ht="409.6">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="9">
-        <v>44330.719444444447</v>
+        <v>44336.390277777777</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F6" s="10">
-        <v>44330</v>
+        <v>44336</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="409.6">
+    <row r="7" spans="1:20" ht="350">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="9">
+        <v>44330.719444444447</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="10">
+        <v>44330</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="409.6">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
         <v>44327.25</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F8" s="2">
         <v>44327</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF409A00-0034-3A43-A521-215CF3C8B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F186900-6A62-AC49-8E96-FA1E189D4120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="0" yWindow="3700" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -646,8 +646,23 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
-&lt;h5&gt;雙北及桃園 2006年以後的規定&lt;/h5&gt;
-但為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
+.&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
+&lt;ol&gt;
+&lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
+&lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
+&lt;li&gt;住戶違反第一項規定，管理負責人或管理委員會應予制止，經制止而不遵從者，應報請主管機關依第四十九條第一項規定處理，該住戶並應於一個月內回復原狀。屆期未回復原狀者，得由管理負責人或管理委員會回復原狀，其費用由該住戶負擔。&lt;/li&gt;
+&lt;/ol&gt;
+&lt;a href="https://www.laws.taipei.gov.tw/Law/LawSearch/LawArticleContent?lawId=P13O1003-20110401&amp;realID=13-15-1003"&gt;臺北市違章建築處理規則&lt;/a&gt;
+&lt;ul&gt;
+&lt;li&gt;第  九  條: 
+建築物依法留設之窗口、陽臺，裝設透空率在百分之七十以上之欄柵式防盜窗，其突出外牆面未超過十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。&lt;br&gt;
+本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
+&lt;li&gt;第  十  條:
+領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
+&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
+為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
 管委會同意且經縣市政府通過可以加窗門窗者，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
 另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
 受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F186900-6A62-AC49-8E96-FA1E189D4120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9A986-8938-8E4A-8E17-B3941E7B200B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3700" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="-1300" yWindow="1340" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -659,11 +659,11 @@
 本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
 &lt;li&gt;第  十  條:
 領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
-&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
+&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。&lt;span style="color:red"&gt; 然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準&lt;/span&gt;。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
 &lt;/ul&gt;
 &lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
 為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
-管委會同意且經縣市政府通過可以加窗門窗者，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
+&lt;span style="color:red"&gt; 管委會同意且經縣市政府通過可以加窗門窗者&lt;/span&gt;，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
 另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
 受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
 &lt;br&gt;&lt;br&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9A986-8938-8E4A-8E17-B3941E7B200B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAC4BF6-D496-EA40-BB02-A1A2509A7C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1300" yWindow="1340" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -631,20 +631,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
-&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
-&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-&lt;br&gt;&lt;br&gt;
-&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
-&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
 .&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
 &lt;ol&gt;
@@ -668,6 +654,20 @@
 受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
 &lt;br&gt;&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
+&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
+&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/574089973221.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
+&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1164,10 +1164,10 @@
         <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="110" customHeight="1">

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAC4BF6-D496-EA40-BB02-A1A2509A7C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32EE51-B576-CF40-9CE8-EBFC40EE66E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -660,7 +660,7 @@
   <si>
     <t xml:space="preserve">&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
 &lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
-&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/574089973221.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
+&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
 &lt;br&gt;&lt;br&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32EE51-B576-CF40-9CE8-EBFC40EE66E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B019028B-E526-8146-90D7-3402599B9BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="1720" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -632,7 +632,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
-.&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
+&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
 &lt;ol&gt;
 &lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
 &lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
@@ -658,7 +658,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
+    <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
+&lt;ul&gt;
+&lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
+&lt;li&gt;台北市規範主要考量是避免住戶將陽台轉為室內空間使用，影響建蔽率與容積率計算。但雙北市寸土寸金的狀況，桃園市房價沒有必要將陽台轉室內使用, 所以桃園市是否要比照雙北規範值得商榷。&lt;/li&gt;
+&lt;li&gt;上龜山處於高地, 颱風季節強風大雨完全沒有屏蔽狀況下，陽台能有防風雨的需求遠大於位處盆地的台北市。尤其是桃園環境垃圾充斥，造成蒼蠅在高摟陽台上揮之不去的困境也非雙北優良環境可相比。&lt;/li&gt;
+&lt;li&gt;社區管委會依據區分所有權人會議決議, 提交之統一樣式加窗申請, 往往都被否決。需要市府/議員 能提供何種樣式才能通過？多數議員都有法律諮詢的服務，應該給予市民共同議題提供協助。 &lt;/li&gt;
+&lt;li&gt;部分居民直接自行在陽台加窗, 是相信市府不會執行強制拆除！ 也就是不合情理的法規，讓市民因不知情或不得不去違法！希望選舉年能有議員能協助處理 &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
 &lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
 &lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B019028B-E526-8146-90D7-3402599B9BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5D86FD-A786-1C4B-BBFD-C87CB411A2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -631,33 +631,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
-&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
-&lt;ol&gt;
-&lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
-&lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
-&lt;li&gt;住戶違反第一項規定，管理負責人或管理委員會應予制止，經制止而不遵從者，應報請主管機關依第四十九條第一項規定處理，該住戶並應於一個月內回復原狀。屆期未回復原狀者，得由管理負責人或管理委員會回復原狀，其費用由該住戶負擔。&lt;/li&gt;
-&lt;/ol&gt;
-&lt;a href="https://www.laws.taipei.gov.tw/Law/LawSearch/LawArticleContent?lawId=P13O1003-20110401&amp;realID=13-15-1003"&gt;臺北市違章建築處理規則&lt;/a&gt;
-&lt;ul&gt;
-&lt;li&gt;第  九  條: 
-建築物依法留設之窗口、陽臺，裝設透空率在百分之七十以上之欄柵式防盜窗，其突出外牆面未超過十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。&lt;br&gt;
-本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
-&lt;li&gt;第  十  條:
-領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
-&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。&lt;span style="color:red"&gt; 然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準&lt;/span&gt;。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
-為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
-&lt;span style="color:red"&gt; 管委會同意且經縣市政府通過可以加窗門窗者&lt;/span&gt;，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
-另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
-受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
-&lt;br&gt;&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
 &lt;ul&gt;
 &lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
@@ -676,6 +649,37 @@
 &lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
+&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
+&lt;ol&gt;
+&lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
+&lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
+&lt;li&gt;住戶違反第一項規定，管理負責人或管理委員會應予制止，經制止而不遵從者，應報請主管機關依第四十九條第一項規定處理，該住戶並應於一個月內回復原狀。屆期未回復原狀者，得由管理負責人或管理委員會回復原狀，其費用由該住戶負擔。&lt;/li&gt;
+&lt;/ol&gt;
+&lt;a href="https://www.laws.taipei.gov.tw/Law/LawSearch/LawArticleContent?lawId=P13O1003-20110401&amp;realID=13-15-1003"&gt;臺北市違章建築處理規則&lt;/a&gt;
+&lt;ul&gt;
+&lt;li&gt;第  九  條: 
+建築物依法留設之窗口、陽臺，裝設透空率在百分之七十以上之欄柵式防盜窗，其突出外牆面未超過十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。&lt;br&gt;
+本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
+&lt;li&gt;第  十  條:
+領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
+&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。&lt;span style="color:red"&gt; 然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準&lt;/span&gt;。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
+參考資料
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://mrjoewang.com/illegal-buildings/?fbclid=IwAR2SeUNZo6mPQ_pr8nSXUZkIWLDplx02CipvhihA0DDdLp3qURGsxEY7RLM"&gt;喬王的投資理財筆記 2022/06/11&lt;/a&gt; 什麼是違章建築？違建要怎麼查詢？用這一招，判斷你的房子是即報即拆、列管緩拆或免拆！ &lt;/li&gt;
+&lt;/ul&gt;
+為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
+&lt;span style="color:red"&gt; 管委會同意且經縣市政府通過可以加窗門窗者&lt;/span&gt;，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
+另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
+受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
+&lt;br&gt;&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1172,10 +1176,10 @@
         <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="110" customHeight="1">

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5D86FD-A786-1C4B-BBFD-C87CB411A2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE92BE1-B617-EA49-96F2-947CA674B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -628,28 +628,6 @@
   </si>
   <si>
     <t>住家陽台是否能加強防風遮雨等功能？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
-&lt;ul&gt;
-&lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
-&lt;li&gt;台北市規範主要考量是避免住戶將陽台轉為室內空間使用，影響建蔽率與容積率計算。但雙北市寸土寸金的狀況，桃園市房價沒有必要將陽台轉室內使用, 所以桃園市是否要比照雙北規範值得商榷。&lt;/li&gt;
-&lt;li&gt;上龜山處於高地, 颱風季節強風大雨完全沒有屏蔽狀況下，陽台能有防風雨的需求遠大於位處盆地的台北市。尤其是桃園環境垃圾充斥，造成蒼蠅在高摟陽台上揮之不去的困境也非雙北優良環境可相比。&lt;/li&gt;
-&lt;li&gt;社區管委會依據區分所有權人會議決議, 提交之統一樣式加窗申請, 往往都被否決。需要市府/議員 能提供何種樣式才能通過？多數議員都有法律諮詢的服務，應該給予市民共同議題提供協助。 &lt;/li&gt;
-&lt;li&gt;部分居民直接自行在陽台加窗, 是相信市府不會執行強制拆除！ 也就是不合情理的法規，讓市民因不知情或不得不去違法！希望選舉年能有議員能協助處理 &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
-&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
-&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-&lt;br&gt;&lt;br&gt;
-&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
-&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -680,6 +658,28 @@
 受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
 &lt;br&gt;&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
+&lt;ul&gt;
+&lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
+&lt;li&gt;台北市規範主要考量是避免住戶將陽台轉為室內空間使用，影響建蔽率與容積率計算。但雙北市寸土寸金的狀況，桃園市房價沒有必要將陽台轉室內使用, 所以桃園市是否要比照雙北規範值得商榷。&lt;/li&gt;
+&lt;li&gt;上龜山處於高地, 颱風季節強風大雨完全沒有屏蔽狀況下，陽台能有防風雨的需求遠大於位處盆地的台北市。尤其是桃園環境垃圾充斥，造成蒼蠅在高摟陽台上揮之不去的困境也非雙北優良環境可相比。&lt;/li&gt;
+&lt;li&gt;社區管委會依據區分所有權人會議決議, 提交之統一樣式加窗申請, 往往都被否決。需要市府/議員 能提供何種樣式才能通過？多數議員都有法律諮詢的服務，應該給予市民共同議題提供協助。 &lt;/li&gt;
+&lt;li&gt;部分居民直接自行在陽台加窗, 因為陽台加窗是屬於 &lt;span style="color:red"&gt;法規例外的免拆違建&lt;/span&gt;！ 也就是不合情理的法規，讓市民因不知情或不得不去違法！希望選舉年能有議員能協助處理 &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
+&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
+&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
+&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1176,10 +1176,10 @@
         <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="110" customHeight="1">

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE92BE1-B617-EA49-96F2-947CA674B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DF5C11-B07A-744F-89B5-07A9004079C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -672,14 +672,31 @@
 &lt;/ul&gt;
 &lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
 &lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
-&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;全開式摺疊窗&lt;/a&gt;, &lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;案例2&lt;/a&gt;, &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;案例3&lt;/a&gt; 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。&lt;br&gt;
+大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;YKKap&lt;/a&gt;  &lt;/li&gt;
+&lt;li&gt;&lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;梅花鋁業 TSK Windows&lt;/a&gt;, &lt;/li&gt;
+&lt;li&gt; &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;双扇折叠无框阳台窗&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
 &lt;br&gt;&lt;br&gt;
 &lt;h5&gt;升降式百葉窗&lt;/h5&gt;
-&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;電動百葉窗&lt;/a&gt; 或 &lt;a href="https://hexins.tw/shutters/"&gt;手動百葉窗&lt;/a&gt; 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。&lt;br&gt;
+能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;Aurotek 綠風戶外升降百葉窗&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt; &lt;a href="https://hexins.tw/shutters/"&gt;HEXINS - 綠風 Ecocolor 升降鋁百葉窗&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;隱藏式紗窗&lt;/h5&gt;
+使用隱藏式紗窗 阻隔蚊蠅入侵。如使用一沙一布設計則可同時作為遮陽作用。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=osj9Endo7N0"&gt;清展 Hiss 隱藏式紗窗&lt;/a&gt;, &lt;a. href="https://www.hiss.com.tw/Detachable-Pleated-Screen.html"&gt;Hiss 官網&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-08.jpeg" class="img-fluid" style="width:300px"&gt;
+&lt;br&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DF5C11-B07A-744F-89B5-07A9004079C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C909C-16A3-1447-97EB-3B219F217C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -674,8 +674,10 @@
 &lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。
 &lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=DP0Vqpldshs"&gt;GCC 玻璃折疊門&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt;&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;YKKap&lt;/a&gt;  &lt;/li&gt;
 &lt;li&gt;&lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;梅花鋁業 TSK Windows&lt;/a&gt;, &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=XP3Ua5dO0Pw"&gt;根旺鋼鋁門窗 - 全開景觀窗&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt; &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;双扇折叠无框阳台窗&lt;/a&gt;  &lt;/li&gt;
 &lt;/ul&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C909C-16A3-1447-97EB-3B219F217C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC09A23-1D78-6F4C-8B55-807DDF0F2D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -692,9 +692,10 @@
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
 &lt;br&gt;&lt;br&gt;
-&lt;h5&gt;隱藏式紗窗&lt;/h5&gt;
+&lt;h5&gt;隱藏式紗窗/遮陽&lt;/h5&gt;
 使用隱藏式紗窗 阻隔蚊蠅入侵。如使用一沙一布設計則可同時作為遮陽作用。
 &lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.facebook.com/creartdeco/"&gt;CreArt DECO 闊佈置 軟裝設計&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=osj9Endo7N0"&gt;清展 Hiss 隱藏式紗窗&lt;/a&gt;, &lt;a. href="https://www.hiss.com.tw/Detachable-Pleated-Screen.html"&gt;Hiss 官網&lt;/a&gt;  &lt;/li&gt;
 &lt;/ul&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-08.jpeg" class="img-fluid" style="width:300px"&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC09A23-1D78-6F4C-8B55-807DDF0F2D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE2ED7C-F9EE-594E-9D0D-D2698695D343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -686,6 +686,7 @@
 &lt;h5&gt;升降式百葉窗&lt;/h5&gt;
 能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。
 &lt;ul&gt;
+&lt;li&gt;&lt;a href="https://hometime.com.tw/"&gt;宏太金屬 HomeTime&lt;/a&gt;  &lt;/li&gt;
 &lt;li&gt;&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;Aurotek 綠風戶外升降百葉窗&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt; &lt;a href="https://hexins.tw/shutters/"&gt;HEXINS - 綠風 Ecocolor 升降鋁百葉窗&lt;/a&gt;  &lt;/li&gt;
 &lt;/ul&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE2ED7C-F9EE-594E-9D0D-D2698695D343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA08EFD4-5154-654D-9C0C-333C8C104653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -674,6 +674,7 @@
 &lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
 大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。
 &lt;ul&gt;
+&lt;li&gt;&lt;a href="https://fb.watch/dK45iIsIdW/"&gt;設計概念&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=DP0Vqpldshs"&gt;GCC 玻璃折疊門&lt;/a&gt; &lt;/li&gt;
 &lt;li&gt;&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;YKKap&lt;/a&gt;  &lt;/li&gt;
 &lt;li&gt;&lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;梅花鋁業 TSK Windows&lt;/a&gt;, &lt;/li&gt;

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA08EFD4-5154-654D-9C0C-333C8C104653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408F93A4-35D9-2245-AE9B-9C0CA8C1D6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
@@ -628,37 +628,6 @@
   </si>
   <si>
     <t>住家陽台是否能加強防風遮雨等功能？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
-&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
-&lt;ol&gt;
-&lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
-&lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
-&lt;li&gt;住戶違反第一項規定，管理負責人或管理委員會應予制止，經制止而不遵從者，應報請主管機關依第四十九條第一項規定處理，該住戶並應於一個月內回復原狀。屆期未回復原狀者，得由管理負責人或管理委員會回復原狀，其費用由該住戶負擔。&lt;/li&gt;
-&lt;/ol&gt;
-&lt;a href="https://www.laws.taipei.gov.tw/Law/LawSearch/LawArticleContent?lawId=P13O1003-20110401&amp;realID=13-15-1003"&gt;臺北市違章建築處理規則&lt;/a&gt;
-&lt;ul&gt;
-&lt;li&gt;第  九  條: 
-建築物依法留設之窗口、陽臺，裝設透空率在百分之七十以上之欄柵式防盜窗，其突出外牆面未超過十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。&lt;br&gt;
-本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
-&lt;li&gt;第  十  條:
-領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
-&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。&lt;span style="color:red"&gt; 然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準&lt;/span&gt;。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
-參考資料
-&lt;ul&gt;
-&lt;li&gt;&lt;a href="https://mrjoewang.com/illegal-buildings/?fbclid=IwAR2SeUNZo6mPQ_pr8nSXUZkIWLDplx02CipvhihA0DDdLp3qURGsxEY7RLM"&gt;喬王的投資理財筆記 2022/06/11&lt;/a&gt; 什麼是違章建築？違建要怎麼查詢？用這一招，判斷你的房子是即報即拆、列管緩拆或免拆！ &lt;/li&gt;
-&lt;/ul&gt;
-為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
-&lt;span style="color:red"&gt; 管委會同意且經縣市政府通過可以加窗門窗者&lt;/span&gt;，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
-另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
-受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
-&lt;br&gt;&lt;br&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -702,6 +671,38 @@
 &lt;/ul&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-08.jpeg" class="img-fluid" style="width:300px"&gt;
 &lt;br&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h3&gt;住家陽台相關法規&lt;/h3&gt;
+&lt;a href="https://law.moj.gov.tw/LawClass/LawSingleRela.aspx?FLNO=8&amp;PCODE=D0070118&amp;ty=L"&gt;公寓大廈管理條例 第8條&lt;/a&gt; 
+&lt;ol&gt;
+&lt;li&gt;公寓大廈周圍上下、外牆面、樓頂平臺及不屬專有部分之防空避難設備，其變更構造、顏色、設置廣告物、鐵鋁窗或其他類似之行為，除應依法令規定辦理外，該公寓大廈規約另有規定或區分所有權人會議已有決議，經向直轄市、縣（市）主管機關完成報備有案者，應受該規約或區分所有權人會議決議之限制。&lt;/li&gt;
+&lt;li&gt;公寓大廈有十二歲以下兒童或六十五歲以上老人之住戶，外牆開口部或陽臺得設置不妨礙逃生且不突出外牆面之防墜設施。防墜設施設置後，設置理由消失且不符前項限制者，區分所有權人應予改善或回復原狀。&lt;/li&gt;
+&lt;li&gt;住戶違反第一項規定，管理負責人或管理委員會應予制止，經制止而不遵從者，應報請主管機關依第四十九條第一項規定處理，該住戶並應於一個月內回復原狀。屆期未回復原狀者，得由管理負責人或管理委員會回復原狀，其費用由該住戶負擔。&lt;/li&gt;
+&lt;/ol&gt;
+&lt;a href="https://www.laws.taipei.gov.tw/Law/LawSearch/LawArticleContent?lawId=P13O1003-20110401&amp;realID=13-15-1003"&gt;臺北市違章建築處理規則&lt;/a&gt;
+&lt;ul&gt;
+&lt;li&gt;第  九  條: 
+建築物依法留設之窗口、陽臺，裝設透空率在百分之七十以上之欄柵式防盜窗，其突出外牆面未超過十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。&lt;br&gt;
+本規則發布施行前已領有建造執照之建築物，裝設透空率在百分之七十以上之欄柵式防盜窗，其淨深未超過六十公分、面臨道路或基地內通路，且留設有效開口而未上鎖者，應拍照列管。前二項有效開口為淨高一百二十公分以上、淨寬七十五公分以上或內切直徑一百公分以上之開口或圓孔。&lt;/li&gt;
+&lt;li&gt;第  十  條:
+領有使用執照之建築物，二樓以上陽臺加窗或一樓陽臺加設鐵捲門、落地門窗，且原有外牆未拆除者，應拍照列管。但建造執照所載發照日為民國九十五年一月一日以後，其陽臺不計入建蔽率、容積率者，應查報拆除。&lt;/li&gt;
+&lt;li&gt;目前新北市與桃園市也跟進臺北市違章建築處理規則的第十條規定，民眾不得在陽台擅自加窗。&lt;span style="color:red"&gt; 然而各地方政府對陽台加窗是否列為違建查報，都有不同的認定標準&lt;/span&gt;。因此民眾應於陽台裝設鋁窗前，確實了解地方機關的法規限制，以免發生爭議。&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h5&gt;雙北及桃園 2006年以後的規範說明&lt;/h5&gt;
+參考資料
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://mrjoewang.com/illegal-buildings/?fbclid=IwAR2SeUNZo6mPQ_pr8nSXUZkIWLDplx02CipvhihA0DDdLp3qURGsxEY7RLM"&gt;喬王的投資理財筆記 2022/06/11&lt;/a&gt; 什麼是違章建築？違建要怎麼查詢？用這一招，判斷你的房子是即報即拆、列管緩拆或免拆！ &lt;/li&gt;
+&lt;li&gt;公視新聞 2022/03/09 &lt;a href="https://www.youtube.com/watch?v=m15ZD1T9vKg"&gt;陽台不可加窗！&lt;/a&gt;  北市新建案1748件違建&lt;/li&gt;
+&lt;/ul&gt;
+為避免民眾在陽台加窗時將內側牆體敲除，把陽台空間轉為室內空間使用，進而影響逃生安全以及建蔽率與容積率的計算，因雙北及桃園市政府，目前對陽台加窗訂有嚴格的法規限制，一旦陽台加窗有違反當地政府法規，一經舉報，就可能有面臨被查報拆除的可能。&lt;br&gt;&lt;br&gt;
+&lt;span style="color:red"&gt; 管委會同意且經縣市政府通過可以加窗門窗者&lt;/span&gt;，最後還得留意加裝的門窗也得符合不能妨礙消防逃生及救災功能，公寓大廈住戶若因私設鐵窗或鋁窗，未留設供消防人員救災之有效開口者，除可通報主管建築機關查處外，大樓管理委員會亦可援引「公寓大廈管理條例」第8條予以制止。&lt;br&gt;&lt;br&gt;
+另外，外牆附設物的尺度應符合主管機關規定，像是「台北市違章建築處理規則」就有規定，建築物依法留設的窗口、陽台或位於防火間隔（巷）之外牆，裝設欄柵式防盜窗者，其透空率應在70％以上，淨深不得超過60公分，且面臨道路或基地內通路者，應留設有效開口並不得上鎖，違反者查報拆除。&lt;br&gt;&lt;br&gt;
+受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
+&lt;br&gt;&lt;br&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1198,10 +1199,10 @@
         <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="110" customHeight="1">

--- a/db/A7XLK-2202-Announcement.xlsx
+++ b/db/A7XLK-2202-Announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408F93A4-35D9-2245-AE9B-9C0CA8C1D6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F435947E-EBF1-1141-9B91-03D4C9FC8EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27780" windowHeight="17500" xr2:uid="{2429D814-D3EB-0547-A821-96A9EAECCF48}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -628,50 +628,6 @@
   </si>
   <si>
     <t>住家陽台是否能加強防風遮雨等功能？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
-&lt;ul&gt;
-&lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
-&lt;li&gt;台北市規範主要考量是避免住戶將陽台轉為室內空間使用，影響建蔽率與容積率計算。但雙北市寸土寸金的狀況，桃園市房價沒有必要將陽台轉室內使用, 所以桃園市是否要比照雙北規範值得商榷。&lt;/li&gt;
-&lt;li&gt;上龜山處於高地, 颱風季節強風大雨完全沒有屏蔽狀況下，陽台能有防風雨的需求遠大於位處盆地的台北市。尤其是桃園環境垃圾充斥，造成蒼蠅在高摟陽台上揮之不去的困境也非雙北優良環境可相比。&lt;/li&gt;
-&lt;li&gt;社區管委會依據區分所有權人會議決議, 提交之統一樣式加窗申請, 往往都被否決。需要市府/議員 能提供何種樣式才能通過？多數議員都有法律諮詢的服務，應該給予市民共同議題提供協助。 &lt;/li&gt;
-&lt;li&gt;部分居民直接自行在陽台加窗, 因為陽台加窗是屬於 &lt;span style="color:red"&gt;法規例外的免拆違建&lt;/span&gt;！ 也就是不合情理的法規，讓市民因不知情或不得不去違法！希望選舉年能有議員能協助處理 &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
-&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
-大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。
-&lt;ul&gt;
-&lt;li&gt;&lt;a href="https://fb.watch/dK45iIsIdW/"&gt;設計概念&lt;/a&gt; &lt;/li&gt;
-&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=DP0Vqpldshs"&gt;GCC 玻璃折疊門&lt;/a&gt; &lt;/li&gt;
-&lt;li&gt;&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;YKKap&lt;/a&gt;  &lt;/li&gt;
-&lt;li&gt;&lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;梅花鋁業 TSK Windows&lt;/a&gt;, &lt;/li&gt;
-&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=XP3Ua5dO0Pw"&gt;根旺鋼鋁門窗 - 全開景觀窗&lt;/a&gt; &lt;/li&gt;
-&lt;li&gt; &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;双扇折叠无框阳台窗&lt;/a&gt;  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-&lt;br&gt;&lt;br&gt;
-&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
-能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。
-&lt;ul&gt;
-&lt;li&gt;&lt;a href="https://hometime.com.tw/"&gt;宏太金屬 HomeTime&lt;/a&gt;  &lt;/li&gt;
-&lt;li&gt;&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;Aurotek 綠風戶外升降百葉窗&lt;/a&gt; &lt;/li&gt;
-&lt;li&gt; &lt;a href="https://hexins.tw/shutters/"&gt;HEXINS - 綠風 Ecocolor 升降鋁百葉窗&lt;/a&gt;  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
-&lt;br&gt;&lt;br&gt;
-&lt;h5&gt;隱藏式紗窗/遮陽&lt;/h5&gt;
-使用隱藏式紗窗 阻隔蚊蠅入侵。如使用一沙一布設計則可同時作為遮陽作用。
-&lt;ul&gt;
-&lt;li&gt;&lt;a href="https://www.facebook.com/creartdeco/"&gt;CreArt DECO 闊佈置 軟裝設計&lt;/a&gt; &lt;/li&gt;
-&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=osj9Endo7N0"&gt;清展 Hiss 隱藏式紗窗&lt;/a&gt;, &lt;a. href="https://www.hiss.com.tw/Detachable-Pleated-Screen.html"&gt;Hiss 官網&lt;/a&gt;  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-08.jpeg" class="img-fluid" style="width:300px"&gt;
-&lt;br&gt;&lt;br&gt;
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -703,6 +659,51 @@
 受限於陽台無法加裝窗戶，容易造成幼童墜樓的意外發生，因此基於提升兒童居家安全，公寓大廈規約範本也增訂規定，讓有12歲以下兒童 或65歲以上老人的住戶，得依規約規定於外牆開口部或陽台設置如防護網、隱形鐵窗等不妨礙逃生且不突出外牆面的防墜設施，但提醒民眾須留意防墜設施設置後，設置理由消失且不符前項限制者，就應改善或回復原狀。
 &lt;br&gt;&lt;br&gt;
 &lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-05.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;&lt;br&gt;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;h5&gt;現況檢討&lt;/h5&gt;
+&lt;ul&gt;
+&lt;li&gt;陽台不能加窗是台北市的規則，並非中央公寓大廈管理條例的規定。而目前桃園市比照台北市的規範執行。&lt;/li&gt;
+&lt;li&gt;台北市規範主要考量是避免住戶將陽台轉為室內空間使用，影響建蔽率與容積率計算。但雙北市寸土寸金的狀況，桃園市房價沒有必要將陽台轉室內使用, 所以桃園市是否要比照雙北規範值得商榷。&lt;/li&gt;
+&lt;li&gt;上龜山處於高地, 颱風季節強風大雨完全沒有屏蔽狀況下，陽台能有防風雨的需求遠大於位處盆地的台北市。尤其是桃園環境垃圾充斥，造成蒼蠅在高摟陽台上揮之不去的困境也非雙北優良環境可相比。&lt;/li&gt;
+&lt;li&gt;社區管委會依據區分所有權人會議決議, 提交之統一樣式加窗申請, 往往都被否決。需要市府/議員 能提供何種樣式才能通過？多數議員都有法律諮詢的服務，應該給予市民共同議題提供協助。 &lt;/li&gt;
+&lt;li&gt;部分居民直接自行在陽台加窗, 因為陽台加窗是屬於 &lt;span style="color:red"&gt;法規例外的免拆違建&lt;/span&gt;！ 也就是不合情理的法規，讓市民因不知情或不得不去違法！希望選舉年能有議員能協助處理 &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3&gt;以下設計是否合乎法規？有待釐清&lt;/h3&gt;
+&lt;h5&gt;全開式摺疊窗&lt;/h5&gt;
+大面積玻璃 整體設計美觀，當有大雨或颱風期間在龜山高地上能阻擋風雨的入侵陽台。同時完全不會阻擋火災逃生或未來大型物件搬運。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://fb.watch/dK45iIsIdW/"&gt;設計概念&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=DP0Vqpldshs"&gt;GCC 玻璃折疊門&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.ykkap.com.tw/pdt01-05.aspx"&gt;YKKap&lt;/a&gt;  &lt;/li&gt;
+&lt;li&gt;&lt;a href="http://www.tsk.tw/products/bifold-doors/"&gt;梅花鋁業 TSK Windows&lt;/a&gt;, &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=XP3Ua5dO0Pw"&gt;根旺鋼鋁門窗 - 全開景觀窗&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt; &lt;a href="https://detail.1688.com/offer/658144992097.html?spm=a261b.2187593.0.0.64be7e53uAmxbn"&gt;双扇折叠无框阳台窗&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-01.png" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-02.png" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;升降式百葉窗&lt;/h5&gt;
+能擋風防雨，加上智慧型電動裝置能自動調節陽光降低室溫。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="http://www.griesser.com.tw/"&gt;美多利電動升降百葉&lt;/a&gt;  &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://hometime.com.tw/"&gt;宏太金屬 HomeTime&lt;/a&gt;  &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.aurotek.com.tw/tw/product/product-detail/c05/62/196"&gt;Aurotek 綠風戶外升降百葉窗&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt; &lt;a href="https://hexins.tw/shutters/"&gt;HEXINS - 綠風 Ecocolor 升降鋁百葉窗&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-03.webp" class="img-fluid" style="width:300px"&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-04.jpeg" class="img-fluid" style="width:300px"&gt;&lt;br&gt;
+&lt;br&gt;&lt;br&gt;
+&lt;h5&gt;隱藏式紗窗/遮陽&lt;/h5&gt;
+使用隱藏式紗窗 阻隔蚊蠅入侵。如使用一沙一布設計則可同時作為遮陽作用。
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://www.facebook.com/creartdeco/"&gt;CreArt DECO 闊佈置 軟裝設計&lt;/a&gt; &lt;/li&gt;
+&lt;li&gt;&lt;a href="https://www.youtube.com/watch?v=osj9Endo7N0"&gt;清展 Hiss 隱藏式紗窗&lt;/a&gt;, &lt;a. href="https://www.hiss.com.tw/Detachable-Pleated-Screen.html"&gt;Hiss 官網&lt;/a&gt;  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;img src="fig/XLK-211-Environment/XLK-221-陽台窗-08.jpeg" class="img-fluid" style="width:300px"&gt;
+&lt;br&gt;&lt;br&gt;
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1199,10 +1200,10 @@
         <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="110" customHeight="1">
